--- a/cet4/result/08_都市恋曲_咖啡馆的甜蜜陷阱/08_都市恋曲_咖啡馆的甜蜜陷阱_学习版.xlsx
+++ b/cet4/result/08_都市恋曲_咖啡馆的甜蜜陷阱/08_都市恋曲_咖啡馆的甜蜜陷阱_学习版.xlsx
@@ -397,941 +397,759 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D53"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>marble</v>
       </c>
       <c r="B2" t="str">
-        <v>marble</v>
+        <v>/ˈmɑːrbl/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>大理石</v>
       </c>
-      <c r="D2" t="str">
-        <v>marble(大理石)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>remarkable</v>
       </c>
       <c r="B3" t="str">
-        <v>remarkable</v>
+        <v>/rɪˈmɑːrkəbl/</v>
       </c>
       <c r="C3" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>非凡的</v>
       </c>
-      <c r="D3" t="str">
-        <v>remarkable(非凡的)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>creative</v>
       </c>
       <c r="B4" t="str">
-        <v>creative</v>
+        <v>/kriˈeɪtɪv/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>创造性的</v>
       </c>
-      <c r="D4" t="str">
-        <v>creative(创造性的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>Canadian</v>
       </c>
       <c r="B5" t="str">
-        <v>Canadian</v>
+        <v>/kəˈneɪdiən/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>加拿大</v>
       </c>
-      <c r="D5" t="str">
-        <v>Canadian(加拿大)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>vest</v>
       </c>
       <c r="B6" t="str">
-        <v>vest</v>
+        <v>/vest/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>背心</v>
       </c>
-      <c r="D6" t="str">
-        <v>vest(背心)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>senior</v>
       </c>
       <c r="B7" t="str">
-        <v>senior</v>
+        <v>/ˈsiːniər/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>高级的</v>
       </c>
-      <c r="D7" t="str">
-        <v>senior(高级的)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>type</v>
       </c>
       <c r="B8" t="str">
-        <v>type</v>
+        <v>/taɪp/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D8" t="str">
         <v>类型</v>
       </c>
-      <c r="D8" t="str">
-        <v>type(类型)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>glorious</v>
       </c>
       <c r="B9" t="str">
-        <v>glorious</v>
+        <v>/ˈɡlɔːriəs/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>辉煌的</v>
       </c>
-      <c r="D9" t="str">
-        <v>glorious(辉煌的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>marvelous</v>
       </c>
       <c r="B10" t="str">
-        <v>marvelous</v>
+        <v>/ˈmɑːrvələs/</v>
       </c>
       <c r="C10" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>了不起的</v>
       </c>
-      <c r="D10" t="str">
-        <v>marvelous(了不起的)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>devil</v>
       </c>
       <c r="B11" t="str">
-        <v>devil</v>
+        <v>/ˈdevl/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D11" t="str">
         <v>魔鬼</v>
       </c>
-      <c r="D11" t="str">
-        <v>devil(魔鬼)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>curve</v>
       </c>
       <c r="B12" t="str">
-        <v>curve</v>
+        <v>/kɜːrv/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>曲线</v>
       </c>
-      <c r="D12" t="str">
-        <v>curve(曲线)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>joke</v>
       </c>
       <c r="B13" t="str">
-        <v>joke</v>
+        <v>/dʒoʊk/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D13" t="str">
         <v>玩笑</v>
       </c>
-      <c r="D13" t="str">
-        <v>joke(玩笑)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>rejoice</v>
       </c>
       <c r="B14" t="str">
-        <v>rejoice</v>
+        <v>/rɪˈdʒɔɪs/</v>
       </c>
       <c r="C14" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D14" t="str">
         <v>高兴</v>
       </c>
-      <c r="D14" t="str">
-        <v>rejoice(高兴)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>minute</v>
       </c>
       <c r="B15" t="str">
-        <v>minute</v>
+        <v>/ˈmɪnɪt/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>分钟</v>
       </c>
-      <c r="D15" t="str">
-        <v>minute(分钟)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>source</v>
       </c>
       <c r="B16" t="str">
-        <v>source</v>
+        <v>/sɔːrs/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>来源</v>
       </c>
-      <c r="D16" t="str">
-        <v>source(来源)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>outdoors</v>
       </c>
       <c r="B17" t="str">
-        <v>outdoors</v>
+        <v>/ˌaʊtˈdɔːrz/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D17" t="str">
         <v>户外</v>
       </c>
-      <c r="D17" t="str">
-        <v>outdoors(户外)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>drawing</v>
       </c>
       <c r="B18" t="str">
-        <v>drawing</v>
+        <v>/ˈdrɔːɪŋ/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D18" t="str">
         <v>图画</v>
       </c>
-      <c r="D18" t="str">
-        <v>drawing(图画)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>fast</v>
       </c>
       <c r="B19" t="str">
-        <v>fast</v>
+        <v>/fæst/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vi./v./adj./adv.</v>
+      </c>
+      <c r="D19" t="str">
         <v>快</v>
       </c>
-      <c r="D19" t="str">
-        <v>fast(快)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>hostess</v>
       </c>
       <c r="B20" t="str">
-        <v>hostess</v>
+        <v>/ˈhoʊstəs/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>女主人</v>
       </c>
-      <c r="D20" t="str">
-        <v>hostess(女主人)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>married</v>
       </c>
       <c r="B21" t="str">
-        <v>married</v>
+        <v>/ˈmærid/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>已婚的</v>
       </c>
-      <c r="D21" t="str">
-        <v>married(已婚的)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>ancestor</v>
       </c>
       <c r="B22" t="str">
-        <v>marble</v>
+        <v>/ˈænsestər/</v>
       </c>
       <c r="C22" t="str">
-        <v>大理石</v>
+        <v>n.</v>
       </c>
       <c r="D22" t="str">
-        <v>marble(大理石)📢</v>
+        <v>祖先</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>mayor</v>
       </c>
       <c r="B23" t="str">
-        <v>ancestor</v>
+        <v>/ˈmeɪər/</v>
       </c>
       <c r="C23" t="str">
-        <v>祖先</v>
+        <v>n.</v>
       </c>
       <c r="D23" t="str">
-        <v>ancestor(祖先)📢</v>
+        <v>市长</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>approve</v>
       </c>
       <c r="B24" t="str">
-        <v>mayor</v>
+        <v>/əˈpruːv/</v>
       </c>
       <c r="C24" t="str">
-        <v>市长</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D24" t="str">
-        <v>mayor(市长)📢</v>
+        <v>批准</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>almost</v>
       </c>
       <c r="B25" t="str">
-        <v>approve</v>
+        <v>/ˈɔːlmoʊst/</v>
       </c>
       <c r="C25" t="str">
-        <v>批准</v>
+        <v>v./adv.</v>
       </c>
       <c r="D25" t="str">
-        <v>approve(批准)📢</v>
+        <v>几乎</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>minor</v>
       </c>
       <c r="B26" t="str">
-        <v>almost</v>
+        <v>/ˈmaɪnər/</v>
       </c>
       <c r="C26" t="str">
-        <v>几乎</v>
+        <v>n./vi./adj.</v>
       </c>
       <c r="D26" t="str">
-        <v>almost(几乎)📢</v>
+        <v>次要的</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>cordial</v>
       </c>
       <c r="B27" t="str">
-        <v>minor</v>
+        <v>/ˈkɔːrdʒəl/</v>
       </c>
       <c r="C27" t="str">
-        <v>次要的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D27" t="str">
-        <v>minor(次要的)📢</v>
+        <v>甜果汁饮料</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>goat</v>
       </c>
       <c r="B28" t="str">
-        <v>cordial</v>
+        <v>/goʊt/</v>
       </c>
       <c r="C28" t="str">
-        <v>甜果汁饮料</v>
+        <v>n.</v>
       </c>
       <c r="D28" t="str">
-        <v>cordial(甜果汁饮料)📢</v>
+        <v>山羊</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>nut</v>
       </c>
       <c r="B29" t="str">
-        <v>goat</v>
+        <v>/nʌt/</v>
       </c>
       <c r="C29" t="str">
-        <v>山羊</v>
+        <v>n./vi.</v>
       </c>
       <c r="D29" t="str">
-        <v>goat(山羊)📢</v>
+        <v>螺母</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>addition</v>
       </c>
       <c r="B30" t="str">
-        <v>nut</v>
+        <v>/əˈdɪʃn/</v>
       </c>
       <c r="C30" t="str">
-        <v>螺母</v>
+        <v>n.</v>
       </c>
       <c r="D30" t="str">
-        <v>nut(螺母)📢</v>
+        <v>增加物</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>connect</v>
       </c>
       <c r="B31" t="str">
-        <v>addition</v>
+        <v>/kəˈnekt/</v>
       </c>
       <c r="C31" t="str">
-        <v>增加物</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>addition(增加物)📢</v>
+        <v>连接</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>dependent</v>
       </c>
       <c r="B32" t="str">
-        <v>connect</v>
+        <v>/dɪˈpendənt/</v>
       </c>
       <c r="C32" t="str">
-        <v>连接</v>
+        <v>n./adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>connect(连接)📢</v>
+        <v>依赖他人者</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>separately</v>
       </c>
       <c r="B33" t="str">
-        <v>dependent</v>
+        <v>/ˈseprətli/</v>
       </c>
       <c r="C33" t="str">
-        <v>依赖他人者</v>
+        <v>v./adv.</v>
       </c>
       <c r="D33" t="str">
-        <v>dependent(依赖他人者)📢</v>
+        <v>分别地</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>argument</v>
       </c>
       <c r="B34" t="str">
-        <v>minor</v>
+        <v>/ˈɑːrɡjumənt/</v>
       </c>
       <c r="C34" t="str">
-        <v>未成年人</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>minor(未成年人)📢</v>
+        <v>争论</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>beloved</v>
       </c>
       <c r="B35" t="str">
-        <v>separately</v>
+        <v>/bɪ'lʌvɪd/</v>
       </c>
       <c r="C35" t="str">
-        <v>分别地</v>
+        <v>n./adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>separately(分别地)📢</v>
+        <v>挚爱的</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>fifteen</v>
       </c>
       <c r="B36" t="str">
-        <v>argument</v>
+        <v>/ˌfɪfˈtiːn/</v>
       </c>
       <c r="C36" t="str">
-        <v>争论</v>
+        <v>n./adj./num.</v>
       </c>
       <c r="D36" t="str">
-        <v>argument(争论)📢</v>
+        <v>十五</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>bound</v>
       </c>
       <c r="B37" t="str">
-        <v>beloved</v>
+        <v>/baʊnd/</v>
       </c>
       <c r="C37" t="str">
-        <v>挚爱的</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D37" t="str">
-        <v>beloved(挚爱的)📢</v>
+        <v>开往...去的</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>fact</v>
       </c>
       <c r="B38" t="str">
-        <v>fifteen</v>
+        <v>/fækt/</v>
       </c>
       <c r="C38" t="str">
-        <v>十五</v>
+        <v>n.</v>
       </c>
       <c r="D38" t="str">
-        <v>fifteen(十五)📢</v>
+        <v>事实</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>what</v>
       </c>
       <c r="B39" t="str">
-        <v>bound</v>
+        <v>/wʌt/</v>
       </c>
       <c r="C39" t="str">
-        <v>开往...去的</v>
+        <v>n./v./adj./adv./pron./int.</v>
       </c>
       <c r="D39" t="str">
-        <v>bound(开往...去的)📢</v>
+        <v>什么</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>interfere</v>
       </c>
       <c r="B40" t="str">
-        <v>fact</v>
+        <v>/ˌɪntərˈfɪr/</v>
       </c>
       <c r="C40" t="str">
-        <v>事实</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>fact(事实)📢</v>
+        <v>干涉</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>mate</v>
       </c>
       <c r="B41" t="str">
-        <v>what</v>
+        <v>/meɪt/</v>
       </c>
       <c r="C41" t="str">
-        <v>什么</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D41" t="str">
-        <v>what(什么)📢</v>
+        <v>配偶</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>murderer</v>
       </c>
       <c r="B42" t="str">
-        <v>devil</v>
+        <v>/ˈmɜːrdərər/</v>
       </c>
       <c r="C42" t="str">
-        <v>魔鬼</v>
+        <v>n.</v>
       </c>
       <c r="D42" t="str">
-        <v>devil(魔鬼)📢</v>
+        <v>凶手</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>chicken</v>
       </c>
       <c r="B43" t="str">
-        <v>interfere</v>
+        <v>/ˈtʃɪkɪn/</v>
       </c>
       <c r="C43" t="str">
-        <v>干涉</v>
+        <v>n./adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>interfere(干涉)📢</v>
+        <v>鸡肉</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>objection</v>
       </c>
       <c r="B44" t="str">
-        <v>mate</v>
+        <v>/əbˈdʒekʃn/</v>
       </c>
       <c r="C44" t="str">
-        <v>配偶</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>mate(配偶)📢</v>
+        <v>异议</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>laser</v>
       </c>
       <c r="B45" t="str">
-        <v>murderer</v>
+        <v>/ˈleɪzər/</v>
       </c>
       <c r="C45" t="str">
-        <v>凶手</v>
+        <v>n.</v>
       </c>
       <c r="D45" t="str">
-        <v>murderer(凶手)📢</v>
+        <v>激光</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>plug</v>
       </c>
       <c r="B46" t="str">
-        <v>chicken</v>
+        <v>/plʌɡ/</v>
       </c>
       <c r="C46" t="str">
-        <v>鸡肉</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>chicken(鸡肉)📢</v>
+        <v>插头</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>plural</v>
       </c>
       <c r="B47" t="str">
-        <v>objection</v>
+        <v>/ˈplʊrəl/</v>
       </c>
       <c r="C47" t="str">
-        <v>异议</v>
+        <v>n./adj.</v>
       </c>
       <c r="D47" t="str">
-        <v>objection(异议)📢</v>
+        <v>多样的</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>principle</v>
       </c>
       <c r="B48" t="str">
-        <v>laser</v>
+        <v>/ˈprɪnsəpl/</v>
       </c>
       <c r="C48" t="str">
-        <v>激光</v>
+        <v>n.</v>
       </c>
       <c r="D48" t="str">
-        <v>laser(激光)📢</v>
+        <v>原则</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>attraction</v>
       </c>
       <c r="B49" t="str">
-        <v>plug</v>
+        <v>/əˈtrækʃn/</v>
       </c>
       <c r="C49" t="str">
-        <v>插头</v>
+        <v>n.</v>
       </c>
       <c r="D49" t="str">
-        <v>plug(插头)📢</v>
+        <v>吸引力</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>from</v>
       </c>
       <c r="B50" t="str">
-        <v>plural</v>
+        <v>/frəm,frʌm,frɑːm/</v>
       </c>
       <c r="C50" t="str">
-        <v>多样的</v>
+        <v>prep.</v>
       </c>
       <c r="D50" t="str">
-        <v>plural(多样的)📢</v>
+        <v>来自</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>disappoint</v>
       </c>
       <c r="B51" t="str">
-        <v>senior</v>
+        <v>/ˌdɪsəˈpɔɪnt/</v>
       </c>
       <c r="C51" t="str">
-        <v>上司</v>
+        <v>vt.</v>
       </c>
       <c r="D51" t="str">
-        <v>senior(上司)📢</v>
+        <v>使失望</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>evolve</v>
       </c>
       <c r="B52" t="str">
-        <v>objection</v>
+        <v>/ɪˈvɑːlv/</v>
       </c>
       <c r="C52" t="str">
-        <v>反对</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D52" t="str">
-        <v>objection(反对)📢</v>
+        <v>发展</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>strength</v>
       </c>
       <c r="B53" t="str">
-        <v>principle</v>
+        <v>/streŋkθ/</v>
       </c>
       <c r="C53" t="str">
-        <v>原则</v>
+        <v>n.</v>
       </c>
       <c r="D53" t="str">
-        <v>principle(原则)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>beloved</v>
-      </c>
-      <c r="C54" t="str">
-        <v>挚爱的</v>
-      </c>
-      <c r="D54" t="str">
-        <v>beloved(挚爱的)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>attraction</v>
-      </c>
-      <c r="C55" t="str">
-        <v>吸引力</v>
-      </c>
-      <c r="D55" t="str">
-        <v>attraction(吸引力)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>addition</v>
-      </c>
-      <c r="C56" t="str">
-        <v>增加物</v>
-      </c>
-      <c r="D56" t="str">
-        <v>addition(增加物)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>from</v>
-      </c>
-      <c r="C57" t="str">
-        <v>来自</v>
-      </c>
-      <c r="D57" t="str">
-        <v>from(来自)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>glorious</v>
-      </c>
-      <c r="C58" t="str">
-        <v>辉煌的</v>
-      </c>
-      <c r="D58" t="str">
-        <v>glorious(辉煌的)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>disappoint</v>
-      </c>
-      <c r="C59" t="str">
-        <v>使失望</v>
-      </c>
-      <c r="D59" t="str">
-        <v>disappoint(使失望)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>drawing</v>
-      </c>
-      <c r="C60" t="str">
-        <v>绘画</v>
-      </c>
-      <c r="D60" t="str">
-        <v>drawing(绘画)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>remarkable</v>
-      </c>
-      <c r="C61" t="str">
-        <v>非凡的</v>
-      </c>
-      <c r="D61" t="str">
-        <v>remarkable(非凡的)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>evolve</v>
-      </c>
-      <c r="C62" t="str">
-        <v>发展</v>
-      </c>
-      <c r="D62" t="str">
-        <v>evolve(发展)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>marvelous</v>
-      </c>
-      <c r="C63" t="str">
-        <v>了不起的</v>
-      </c>
-      <c r="D63" t="str">
-        <v>marvelous(了不起的)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>strength</v>
-      </c>
-      <c r="C64" t="str">
         <v>力量</v>
-      </c>
-      <c r="D64" t="str">
-        <v>strength(力量)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>devil</v>
-      </c>
-      <c r="C65" t="str">
-        <v>魔鬼</v>
-      </c>
-      <c r="D65" t="str">
-        <v>devil(魔鬼)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>bound</v>
-      </c>
-      <c r="C66" t="str">
-        <v>被束缚的</v>
-      </c>
-      <c r="D66" t="str">
-        <v>bound(被束缚的)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
   </ignoredErrors>
 </worksheet>
 </file>